--- a/tams-invest-parent/tams-invest-entrust/src/main/resources/tpl/EtrBrowDepoInfo002.xlsx
+++ b/tams-invest-parent/tams-invest-entrust/src/main/resources/tpl/EtrBrowDepoInfo002.xlsx
@@ -3,6 +3,11 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\IdeaProjects\GUANGZHOU\tams\tams-invest-parent\tams-invest-entrust\src\main\resources\tpl\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="12915" windowHeight="5985"/>
   </bookViews>
@@ -12,12 +17,11 @@
     <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="0"/>
-  <oleSize ref="A1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
   <si>
     <t>组合代码</t>
   </si>
@@ -70,6 +74,10 @@
   <si>
     <t>资产三级分类</t>
     <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>当前处理人</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -504,6 +512,9 @@
       <c r="P1" t="s">
         <v>11</v>
       </c>
+      <c r="Q1" t="s">
+        <v>16</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
